--- a/Data/Home/BedroomTwo.Brightness.xlsx
+++ b/Data/Home/BedroomTwo.Brightness.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H252"/>
+  <dimension ref="A1:I262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709248401</v>
+        <v>1711840701</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -501,6 +506,7 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709248412</v>
+        <v>1711840711</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -533,6 +539,7 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,7 +558,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709248425</v>
+        <v>1711840721</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -565,6 +572,7 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,7 +591,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709250371</v>
+        <v>1711842311</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -597,6 +605,7 @@
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,7 +624,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709250383</v>
+        <v>1711842326</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -629,6 +638,7 @@
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,7 +657,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709250401</v>
+        <v>1711842335</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -661,6 +671,7 @@
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,7 +690,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709250977</v>
+        <v>1711843358</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -693,6 +704,7 @@
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -711,7 +723,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709250989</v>
+        <v>1711843375</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -725,6 +737,7 @@
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -743,7 +756,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709251005</v>
+        <v>1711843389</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -757,6 +770,7 @@
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -775,7 +789,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709252258</v>
+        <v>1711845252</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -789,6 +803,7 @@
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -807,7 +822,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709252283</v>
+        <v>1711845269</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -821,6 +836,7 @@
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -839,7 +855,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709252302</v>
+        <v>1711845291</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -853,6 +869,7 @@
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -871,7 +888,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709259225</v>
+        <v>1711852891</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -885,6 +902,7 @@
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -903,7 +921,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709259261</v>
+        <v>1711852906</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -917,6 +935,7 @@
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -935,7 +954,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709259294</v>
+        <v>1711852929</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -949,6 +968,11 @@
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -967,7 +991,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709244477</v>
+        <v>1711927569</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -981,6 +1005,7 @@
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -999,7 +1024,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709244519</v>
+        <v>1711927590</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1013,6 +1038,7 @@
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1031,7 +1057,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709244544</v>
+        <v>1711927605</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1045,6 +1071,7 @@
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1063,7 +1090,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709244680</v>
+        <v>1711928263</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1077,6 +1104,7 @@
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1095,7 +1123,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709244710</v>
+        <v>1711928275</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1109,6 +1137,7 @@
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1127,7 +1156,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709244737</v>
+        <v>1711928288</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1141,6 +1170,7 @@
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1159,7 +1189,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709246055</v>
+        <v>1711930007</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1173,6 +1203,7 @@
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1191,7 +1222,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709246090</v>
+        <v>1711930025</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1205,6 +1236,7 @@
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1223,7 +1255,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709246117</v>
+        <v>1711930056</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1237,6 +1269,7 @@
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1255,7 +1288,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709252568</v>
+        <v>1711937842</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1269,6 +1302,7 @@
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1287,7 +1321,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709252600</v>
+        <v>1711937870</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1301,6 +1335,7 @@
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1319,7 +1354,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709252636</v>
+        <v>1711937911</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1333,6 +1368,11 @@
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1351,7 +1391,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709330168</v>
+        <v>1712015060</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1365,6 +1405,7 @@
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1383,7 +1424,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709330188</v>
+        <v>1712015074</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1397,6 +1438,7 @@
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1415,7 +1457,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709330215</v>
+        <v>1712015089</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1429,6 +1471,7 @@
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1447,7 +1490,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709330475</v>
+        <v>1712016898</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1461,6 +1504,7 @@
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1479,7 +1523,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1709330502</v>
+        <v>1712016910</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1493,6 +1537,7 @@
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1511,7 +1556,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1709330524</v>
+        <v>1712016928</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1525,6 +1570,7 @@
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1543,7 +1589,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1709331864</v>
+        <v>1712019057</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1557,6 +1603,7 @@
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1575,7 +1622,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1709331899</v>
+        <v>1712019069</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1589,6 +1636,7 @@
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1607,7 +1655,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1709331927</v>
+        <v>1712019093</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1621,6 +1669,7 @@
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1639,7 +1688,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1709338706</v>
+        <v>1712019115</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1653,6 +1702,7 @@
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1671,7 +1721,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1709338744</v>
+        <v>1712019140</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1685,6 +1735,7 @@
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1703,7 +1754,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1709338790</v>
+        <v>1712019163</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1717,6 +1768,11 @@
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1735,7 +1791,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1709417085</v>
+        <v>1712101498</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1749,6 +1805,7 @@
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1767,7 +1824,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1709417109</v>
+        <v>1712101513</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1781,6 +1838,7 @@
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1799,7 +1857,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1709417134</v>
+        <v>1712101523</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1813,6 +1871,7 @@
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1831,7 +1890,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1709417227</v>
+        <v>1712101985</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1845,6 +1904,7 @@
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1863,7 +1923,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1709417251</v>
+        <v>1712101995</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1877,6 +1937,7 @@
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1895,7 +1956,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1709417284</v>
+        <v>1712102005</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1909,6 +1970,7 @@
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1927,7 +1989,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1709418488</v>
+        <v>1712103708</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1941,6 +2003,7 @@
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1959,7 +2022,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1709418524</v>
+        <v>1712103723</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1973,6 +2036,7 @@
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1991,7 +2055,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1709418549</v>
+        <v>1712103735</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2005,6 +2069,7 @@
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2023,7 +2088,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1709425422</v>
+        <v>1712112823</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2037,6 +2102,7 @@
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2055,7 +2121,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1709425463</v>
+        <v>1712112838</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2069,6 +2135,7 @@
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2087,7 +2154,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1709425509</v>
+        <v>1712112862</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2101,6 +2168,11 @@
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2119,7 +2191,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1709502413</v>
+        <v>1712187811</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2133,6 +2205,7 @@
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2151,7 +2224,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1709502445</v>
+        <v>1712187825</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2165,6 +2238,7 @@
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2183,7 +2257,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1709502467</v>
+        <v>1712187836</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2197,6 +2271,7 @@
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2215,7 +2290,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1709502864</v>
+        <v>1712188366</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2229,6 +2304,7 @@
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2247,7 +2323,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1709502883</v>
+        <v>1712188377</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2261,6 +2337,7 @@
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2279,7 +2356,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1709502901</v>
+        <v>1712188389</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2293,6 +2370,7 @@
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2311,7 +2389,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1709504124</v>
+        <v>1712190071</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2325,6 +2403,7 @@
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2343,7 +2422,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1709504151</v>
+        <v>1712190100</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2357,6 +2436,7 @@
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2375,7 +2455,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1709504187</v>
+        <v>1712190129</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2389,6 +2469,7 @@
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2407,7 +2488,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1709511549</v>
+        <v>1712199706</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2421,6 +2502,7 @@
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2439,7 +2521,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1709511578</v>
+        <v>1712199728</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2453,6 +2535,7 @@
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2471,7 +2554,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1709511603</v>
+        <v>1712199748</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2485,6 +2568,11 @@
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2503,7 +2591,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1709588928</v>
+        <v>1712274240</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2517,6 +2605,7 @@
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2535,7 +2624,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1709588950</v>
+        <v>1712274258</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2549,6 +2638,7 @@
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2567,7 +2657,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1709588981</v>
+        <v>1712274267</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2581,6 +2671,7 @@
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2599,7 +2690,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1709589535</v>
+        <v>1712275739</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2613,6 +2704,7 @@
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2631,7 +2723,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1709589554</v>
+        <v>1712275758</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2645,6 +2737,7 @@
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2663,7 +2756,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1709589574</v>
+        <v>1712275776</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2677,6 +2770,7 @@
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2695,7 +2789,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1709590950</v>
+        <v>1712278058</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2709,6 +2803,7 @@
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2727,7 +2822,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1709590979</v>
+        <v>1712278070</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2741,6 +2836,7 @@
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2759,7 +2855,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1709591005</v>
+        <v>1712278081</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2773,6 +2869,7 @@
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2791,7 +2888,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1709598810</v>
+        <v>1712283571</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2805,6 +2902,7 @@
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2823,7 +2921,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1709598854</v>
+        <v>1712283585</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2837,6 +2935,7 @@
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2855,7 +2954,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1709598883</v>
+        <v>1712283601</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2869,6 +2968,11 @@
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2887,7 +2991,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1709848901</v>
+        <v>1712533229</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2901,6 +3005,7 @@
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2919,7 +3024,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1709848940</v>
+        <v>1712533247</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2933,6 +3038,7 @@
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2951,7 +3057,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1709848972</v>
+        <v>1712533266</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2965,6 +3071,7 @@
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2983,7 +3090,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1709850716</v>
+        <v>1712533877</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2997,6 +3104,7 @@
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3015,7 +3123,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1709850742</v>
+        <v>1712533888</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3029,6 +3137,7 @@
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3047,7 +3156,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1709850778</v>
+        <v>1712533897</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3061,6 +3170,7 @@
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3079,7 +3189,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1709852258</v>
+        <v>1712535494</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3093,6 +3203,7 @@
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3111,7 +3222,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1709852289</v>
+        <v>1712535513</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3125,6 +3236,7 @@
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3143,7 +3255,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1709852317</v>
+        <v>1712535526</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3157,6 +3269,7 @@
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3175,7 +3288,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1709852347</v>
+        <v>1712544390</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3189,6 +3302,7 @@
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3207,7 +3321,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1709852383</v>
+        <v>1712544409</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3221,6 +3335,7 @@
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3239,7 +3354,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1709852420</v>
+        <v>1712544425</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3253,6 +3368,11 @@
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3271,7 +3391,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1709936025</v>
+        <v>1712619635</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3285,6 +3405,7 @@
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3303,7 +3424,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1709936052</v>
+        <v>1712619650</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3317,6 +3438,7 @@
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3335,7 +3457,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1709936070</v>
+        <v>1712619666</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3349,6 +3471,7 @@
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3367,7 +3490,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1709936881</v>
+        <v>1712621676</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3381,6 +3504,7 @@
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3399,7 +3523,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1709936912</v>
+        <v>1712621702</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3413,6 +3537,7 @@
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3431,7 +3556,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1709936933</v>
+        <v>1712621721</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3441,10 +3566,11 @@
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>BedroomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3463,7 +3589,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1709938157</v>
+        <v>1712622266</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3477,6 +3603,7 @@
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3495,7 +3622,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1709938187</v>
+        <v>1712622278</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3505,10 +3632,11 @@
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dim</t>
+          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3527,7 +3655,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1709938215</v>
+        <v>1712623973</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3537,10 +3665,11 @@
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dark</t>
+          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3559,7 +3688,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1709944021</v>
+        <v>1712623989</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3573,6 +3702,7 @@
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3591,7 +3721,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1709944054</v>
+        <v>1712624005</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3601,10 +3731,11 @@
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>BedroomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3623,7 +3754,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1709944086</v>
+        <v>1712630710</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3633,10 +3764,11 @@
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>BedroomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3655,7 +3787,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1710022249</v>
+        <v>1712630733</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3669,6 +3801,7 @@
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3687,7 +3820,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1710022274</v>
+        <v>1712630754</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3697,10 +3830,15 @@
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dim</t>
+          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3719,7 +3857,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1710022311</v>
+        <v>1712705988</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3729,10 +3867,11 @@
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dark</t>
+          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3751,7 +3890,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1710022590</v>
+        <v>1712706004</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3765,6 +3904,7 @@
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3783,7 +3923,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1710022615</v>
+        <v>1712706019</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3793,10 +3933,11 @@
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>BedroomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3815,7 +3956,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1710022631</v>
+        <v>1712706369</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3825,10 +3966,11 @@
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>BedroomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3847,7 +3989,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1710023912</v>
+        <v>1712706380</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3861,6 +4003,7 @@
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3879,7 +4022,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1710023945</v>
+        <v>1712706392</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3889,10 +4032,11 @@
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dim</t>
+          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3911,7 +4055,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1710023976</v>
+        <v>1712708130</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3921,10 +4065,11 @@
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dark</t>
+          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3943,7 +4088,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1710031546</v>
+        <v>1712708142</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3957,6 +4102,7 @@
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3975,7 +4121,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1710031586</v>
+        <v>1712708172</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3985,10 +4131,11 @@
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>BedroomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4007,7 +4154,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1710031631</v>
+        <v>1712716152</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4017,10 +4164,11 @@
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>BedroomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4039,7 +4187,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1710107827</v>
+        <v>1712716169</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -4053,6 +4201,7 @@
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4071,7 +4220,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1710107847</v>
+        <v>1712716187</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4081,10 +4230,15 @@
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dim</t>
+          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4103,7 +4257,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1710107879</v>
+        <v>1712791432</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4113,10 +4267,11 @@
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dark</t>
+          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4135,7 +4290,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1710107917</v>
+        <v>1712791449</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4149,6 +4304,7 @@
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4167,7 +4323,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1710107932</v>
+        <v>1712791460</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4177,10 +4333,11 @@
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>BedroomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4199,7 +4356,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1710107965</v>
+        <v>1712792166</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4209,10 +4366,11 @@
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>BedroomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4231,7 +4389,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1710109194</v>
+        <v>1712792175</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4245,6 +4403,7 @@
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4263,7 +4422,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1710109215</v>
+        <v>1712792187</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4273,10 +4432,11 @@
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dim</t>
+          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4295,7 +4455,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1710109233</v>
+        <v>1712793845</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4305,10 +4465,11 @@
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dark</t>
+          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4327,7 +4488,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1710117389</v>
+        <v>1712793863</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4341,6 +4502,7 @@
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4359,7 +4521,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1710117419</v>
+        <v>1712793884</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4369,10 +4531,11 @@
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>BedroomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4391,7 +4554,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1710117447</v>
+        <v>1712802583</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4401,10 +4564,11 @@
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>BedroomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4423,7 +4587,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1710196023</v>
+        <v>1712802607</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4437,6 +4601,7 @@
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4455,7 +4620,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1710196054</v>
+        <v>1712802625</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4465,10 +4630,15 @@
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dim</t>
+          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4487,7 +4657,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1710196071</v>
+        <v>1712878063</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4497,10 +4667,11 @@
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dark</t>
+          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4519,7 +4690,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1710196937</v>
+        <v>1712878078</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4533,6 +4704,7 @@
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4551,7 +4723,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1710196961</v>
+        <v>1712878092</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4561,10 +4733,11 @@
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>BedroomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4583,7 +4756,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1710196979</v>
+        <v>1712878336</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4593,10 +4766,11 @@
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>BedroomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4615,7 +4789,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1710198509</v>
+        <v>1712878346</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4629,6 +4803,7 @@
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4647,7 +4822,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1710198532</v>
+        <v>1712878356</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4657,10 +4832,11 @@
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dim</t>
+          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4679,7 +4855,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1710198564</v>
+        <v>1712880088</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4689,10 +4865,11 @@
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dark</t>
+          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4711,7 +4888,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1710206460</v>
+        <v>1712880101</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4725,6 +4902,7 @@
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4743,7 +4921,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1710206487</v>
+        <v>1712880119</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -4753,10 +4931,11 @@
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>BedroomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4775,7 +4954,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1710206520</v>
+        <v>1712889616</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4785,10 +4964,11 @@
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>BedroomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4807,7 +4987,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1710455789</v>
+        <v>1712889637</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4821,6 +5001,7 @@
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4839,7 +5020,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1710455814</v>
+        <v>1712889662</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4849,10 +5030,15 @@
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dim</t>
+          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4871,7 +5057,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1710455841</v>
+        <v>1713137987</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4881,10 +5067,11 @@
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dark</t>
+          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4903,7 +5090,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1710456208</v>
+        <v>1713138005</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -4917,6 +5104,7 @@
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4935,7 +5123,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1710456225</v>
+        <v>1713138016</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -4945,10 +5133,11 @@
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>BedroomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4967,7 +5156,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1710456249</v>
+        <v>1713138372</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -4977,10 +5166,11 @@
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>BedroomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4999,7 +5189,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1710457734</v>
+        <v>1713138382</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -5013,6 +5203,7 @@
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5031,7 +5222,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1710457755</v>
+        <v>1713138392</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -5041,10 +5232,11 @@
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dim</t>
+          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5063,7 +5255,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1710457786</v>
+        <v>1713140102</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -5073,10 +5265,11 @@
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dark</t>
+          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5095,7 +5288,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1710464885</v>
+        <v>1713140117</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -5109,6 +5302,7 @@
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5127,7 +5321,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1710464907</v>
+        <v>1713140137</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -5137,10 +5331,11 @@
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>BedroomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5159,7 +5354,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1710464951</v>
+        <v>1713147632</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -5169,10 +5364,11 @@
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>BedroomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5191,7 +5387,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1710540883</v>
+        <v>1713147649</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -5205,6 +5401,7 @@
         </is>
       </c>
       <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5223,7 +5420,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1710540908</v>
+        <v>1713147674</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -5233,10 +5430,15 @@
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dim</t>
+          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5255,7 +5457,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1710540929</v>
+        <v>1713224169</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -5265,10 +5467,11 @@
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dark</t>
+          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5287,7 +5490,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1710548132</v>
+        <v>1713224190</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -5301,6 +5504,7 @@
         </is>
       </c>
       <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5319,7 +5523,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1710548165</v>
+        <v>1713224202</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -5329,10 +5533,11 @@
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>BedroomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5351,7 +5556,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1710548212</v>
+        <v>1713224710</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -5361,10 +5566,11 @@
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>BedroomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5383,7 +5589,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1710626829</v>
+        <v>1713224720</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -5397,6 +5603,7 @@
         </is>
       </c>
       <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5415,7 +5622,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1710626852</v>
+        <v>1713224731</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -5425,10 +5632,11 @@
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dim</t>
+          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5447,7 +5655,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1710626877</v>
+        <v>1713226465</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -5457,10 +5665,11 @@
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dark</t>
+          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5479,7 +5688,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1710627292</v>
+        <v>1713226481</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -5493,6 +5702,7 @@
         </is>
       </c>
       <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5511,7 +5721,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1710627316</v>
+        <v>1713226493</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -5521,10 +5731,11 @@
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>BedroomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5543,7 +5754,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1710627348</v>
+        <v>1713236676</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -5553,10 +5764,11 @@
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>BedroomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5575,7 +5787,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1710628520</v>
+        <v>1713236690</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -5589,6 +5801,7 @@
         </is>
       </c>
       <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5607,7 +5820,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1710628546</v>
+        <v>1713236707</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -5617,10 +5830,15 @@
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dim</t>
+          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5639,7 +5857,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1710628582</v>
+        <v>1713310801</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -5649,10 +5867,11 @@
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dark</t>
+          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5671,7 +5890,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1710635421</v>
+        <v>1713310821</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -5685,6 +5904,7 @@
         </is>
       </c>
       <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5703,7 +5923,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1710635476</v>
+        <v>1713310833</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -5713,10 +5933,11 @@
       <c r="F165" t="inlineStr"/>
       <c r="G165" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>BedroomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5735,7 +5956,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1710635512</v>
+        <v>1713312147</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -5745,10 +5966,11 @@
       <c r="F166" t="inlineStr"/>
       <c r="G166" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>BedroomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5767,7 +5989,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1710713342</v>
+        <v>1713312162</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -5781,6 +6003,7 @@
         </is>
       </c>
       <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5799,7 +6022,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>1710713370</v>
+        <v>1713312178</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -5813,6 +6036,7 @@
         </is>
       </c>
       <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5831,7 +6055,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>1710713389</v>
+        <v>1713312764</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -5841,10 +6065,11 @@
       <c r="F169" t="inlineStr"/>
       <c r="G169" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dark</t>
+          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -5863,7 +6088,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1710713924</v>
+        <v>1713312776</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -5873,10 +6098,11 @@
       <c r="F170" t="inlineStr"/>
       <c r="G170" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dim</t>
+          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5895,7 +6121,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>1710713945</v>
+        <v>1713314470</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -5909,6 +6135,7 @@
         </is>
       </c>
       <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5927,7 +6154,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1710713968</v>
+        <v>1713314484</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -5937,10 +6164,11 @@
       <c r="F172" t="inlineStr"/>
       <c r="G172" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>BedroomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5959,7 +6187,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1710715534</v>
+        <v>1713314502</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -5969,10 +6197,11 @@
       <c r="F173" t="inlineStr"/>
       <c r="G173" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>BedroomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5991,7 +6220,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1710715581</v>
+        <v>1713322207</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -6005,6 +6234,7 @@
         </is>
       </c>
       <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6023,7 +6253,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1710715614</v>
+        <v>1713322224</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -6033,10 +6263,11 @@
       <c r="F175" t="inlineStr"/>
       <c r="G175" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dark</t>
+          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6055,7 +6286,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1710723085</v>
+        <v>1713322247</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -6065,10 +6296,15 @@
       <c r="F176" t="inlineStr"/>
       <c r="G176" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dim</t>
+          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6087,7 +6323,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>1710723125</v>
+        <v>1713396649</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -6101,6 +6337,7 @@
         </is>
       </c>
       <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6119,7 +6356,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>1710723157</v>
+        <v>1713396672</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -6129,10 +6366,11 @@
       <c r="F178" t="inlineStr"/>
       <c r="G178" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>BedroomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6151,7 +6389,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>1710799478</v>
+        <v>1713396684</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -6161,10 +6399,11 @@
       <c r="F179" t="inlineStr"/>
       <c r="G179" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>BedroomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6183,7 +6422,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>1710799502</v>
+        <v>1713397055</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -6197,6 +6436,7 @@
         </is>
       </c>
       <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6215,7 +6455,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>1710799526</v>
+        <v>1713397067</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -6225,10 +6465,11 @@
       <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dark</t>
+          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6247,7 +6488,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>1710799736</v>
+        <v>1713397080</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -6257,10 +6498,11 @@
       <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dim</t>
+          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -6279,7 +6521,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>1710799766</v>
+        <v>1713398924</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -6293,6 +6535,7 @@
         </is>
       </c>
       <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -6311,7 +6554,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>1710799798</v>
+        <v>1713398940</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -6321,10 +6564,11 @@
       <c r="F184" t="inlineStr"/>
       <c r="G184" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>BedroomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6343,7 +6587,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>1710801205</v>
+        <v>1713398961</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -6353,10 +6597,11 @@
       <c r="F185" t="inlineStr"/>
       <c r="G185" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>BedroomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6375,7 +6620,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>1710801237</v>
+        <v>1713406757</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -6389,6 +6634,7 @@
         </is>
       </c>
       <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -6407,7 +6653,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>1710801272</v>
+        <v>1713406780</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -6417,10 +6663,11 @@
       <c r="F187" t="inlineStr"/>
       <c r="G187" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dark</t>
+          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -6439,7 +6686,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>1710807855</v>
+        <v>1713406807</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -6449,10 +6696,15 @@
       <c r="F188" t="inlineStr"/>
       <c r="G188" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dim</t>
+          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -6471,7 +6723,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>1710807888</v>
+        <v>1713483265</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -6485,6 +6737,7 @@
         </is>
       </c>
       <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -6503,7 +6756,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>1710807926</v>
+        <v>1713483284</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -6513,10 +6766,11 @@
       <c r="F190" t="inlineStr"/>
       <c r="G190" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>BedroomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6535,7 +6789,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>1711059206</v>
+        <v>1713483299</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -6545,10 +6799,11 @@
       <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>BedroomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6567,7 +6822,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>1711059244</v>
+        <v>1713485399</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -6581,6 +6836,7 @@
         </is>
       </c>
       <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -6599,7 +6855,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>1711059274</v>
+        <v>1713485417</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -6609,10 +6865,11 @@
       <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dark</t>
+          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -6631,7 +6888,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>1711059890</v>
+        <v>1713485440</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -6641,10 +6898,11 @@
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dim</t>
+          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -6663,7 +6921,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>1711059907</v>
+        <v>1713487626</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -6677,6 +6935,7 @@
         </is>
       </c>
       <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -6695,7 +6954,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>1711059935</v>
+        <v>1713487644</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -6705,10 +6964,11 @@
       <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>BedroomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -6727,7 +6987,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>1711061392</v>
+        <v>1713487667</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -6737,10 +6997,11 @@
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>BedroomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -6759,7 +7020,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>1711061443</v>
+        <v>1713487699</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -6773,6 +7034,7 @@
         </is>
       </c>
       <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -6791,7 +7053,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>1711061474</v>
+        <v>1713487719</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -6801,10 +7063,11 @@
       <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dark</t>
+          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -6823,7 +7086,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>1711067734</v>
+        <v>1713487736</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -6833,10 +7096,15 @@
       <c r="F200" t="inlineStr"/>
       <c r="G200" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dim</t>
+          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -6855,7 +7123,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>1711067765</v>
+        <v>1713741249</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -6869,6 +7137,7 @@
         </is>
       </c>
       <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -6887,7 +7156,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>1711067807</v>
+        <v>1713741276</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -6897,10 +7166,11 @@
       <c r="F202" t="inlineStr"/>
       <c r="G202" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>BedroomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -6919,7 +7189,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>1711145656</v>
+        <v>1713741292</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -6929,10 +7199,11 @@
       <c r="F203" t="inlineStr"/>
       <c r="G203" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>BedroomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -6951,7 +7222,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>1711145684</v>
+        <v>1713742039</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -6965,6 +7236,7 @@
         </is>
       </c>
       <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -6983,7 +7255,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>1711145712</v>
+        <v>1713742051</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -6993,10 +7265,11 @@
       <c r="F205" t="inlineStr"/>
       <c r="G205" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dark</t>
+          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -7015,7 +7288,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>1711146037</v>
+        <v>1713742065</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -7025,10 +7298,11 @@
       <c r="F206" t="inlineStr"/>
       <c r="G206" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dim</t>
+          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -7047,7 +7321,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>1711146063</v>
+        <v>1713743850</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -7061,6 +7335,7 @@
         </is>
       </c>
       <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -7079,7 +7354,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>1711146088</v>
+        <v>1713743864</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -7089,10 +7364,11 @@
       <c r="F208" t="inlineStr"/>
       <c r="G208" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>BedroomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -7111,7 +7387,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>1711147609</v>
+        <v>1713743880</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -7121,10 +7397,11 @@
       <c r="F209" t="inlineStr"/>
       <c r="G209" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>BedroomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -7143,7 +7420,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>1711147642</v>
+        <v>1713752013</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -7157,6 +7434,7 @@
         </is>
       </c>
       <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -7175,7 +7453,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>1711147678</v>
+        <v>1713752032</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -7185,10 +7463,11 @@
       <c r="F211" t="inlineStr"/>
       <c r="G211" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dark</t>
+          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -7207,7 +7486,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>1711153731</v>
+        <v>1713752052</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -7217,10 +7496,15 @@
       <c r="F212" t="inlineStr"/>
       <c r="G212" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dim</t>
+          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -7239,7 +7523,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>1711153763</v>
+        <v>1713828718</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -7253,6 +7537,7 @@
         </is>
       </c>
       <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -7271,7 +7556,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>1711153802</v>
+        <v>1713828737</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -7281,10 +7566,11 @@
       <c r="F214" t="inlineStr"/>
       <c r="G214" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>BedroomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -7303,7 +7589,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>1711233389</v>
+        <v>1713828755</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -7313,10 +7599,11 @@
       <c r="F215" t="inlineStr"/>
       <c r="G215" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>BedroomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -7335,7 +7622,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>1711233439</v>
+        <v>1713830438</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -7349,6 +7636,7 @@
         </is>
       </c>
       <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -7367,7 +7655,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>1711233472</v>
+        <v>1713830471</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -7377,10 +7665,11 @@
       <c r="F217" t="inlineStr"/>
       <c r="G217" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dark</t>
+          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -7399,7 +7688,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>1711234633</v>
+        <v>1713830509</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -7409,10 +7698,11 @@
       <c r="F218" t="inlineStr"/>
       <c r="G218" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dim</t>
+          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -7431,7 +7721,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>1711235142</v>
+        <v>1713832772</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -7445,6 +7735,7 @@
         </is>
       </c>
       <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -7463,7 +7754,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>1711235164</v>
+        <v>1713832786</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -7473,10 +7764,11 @@
       <c r="F220" t="inlineStr"/>
       <c r="G220" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>BedroomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -7495,7 +7787,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>1711236680</v>
+        <v>1713832804</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -7505,10 +7797,11 @@
       <c r="F221" t="inlineStr"/>
       <c r="G221" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>BedroomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -7527,7 +7820,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>1711236711</v>
+        <v>1713832822</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -7541,6 +7834,7 @@
         </is>
       </c>
       <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -7559,7 +7853,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>1711236730</v>
+        <v>1713832843</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -7569,10 +7863,11 @@
       <c r="F223" t="inlineStr"/>
       <c r="G223" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dark</t>
+          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -7591,7 +7886,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>1711242921</v>
+        <v>1713832858</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -7601,10 +7896,15 @@
       <c r="F224" t="inlineStr"/>
       <c r="G224" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dim</t>
+          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -7623,7 +7923,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>1711242963</v>
+        <v>1713915454</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -7637,6 +7937,7 @@
         </is>
       </c>
       <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -7655,7 +7956,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>1711242993</v>
+        <v>1713915472</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -7665,10 +7966,11 @@
       <c r="F226" t="inlineStr"/>
       <c r="G226" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>BedroomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -7687,7 +7989,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>1711319820</v>
+        <v>1713915485</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
@@ -7697,10 +7999,11 @@
       <c r="F227" t="inlineStr"/>
       <c r="G227" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>BedroomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -7719,7 +8022,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>1711319844</v>
+        <v>1713915843</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -7733,6 +8036,7 @@
         </is>
       </c>
       <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -7751,7 +8055,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>1711319876</v>
+        <v>1713915853</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
@@ -7761,10 +8065,11 @@
       <c r="F229" t="inlineStr"/>
       <c r="G229" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dark</t>
+          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -7783,7 +8088,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>1711321064</v>
+        <v>1713915863</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -7793,10 +8098,11 @@
       <c r="F230" t="inlineStr"/>
       <c r="G230" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dim</t>
+          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -7815,7 +8121,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>1711321087</v>
+        <v>1713917512</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -7829,6 +8135,7 @@
         </is>
       </c>
       <c r="H231" t="inlineStr"/>
+      <c r="I231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -7847,7 +8154,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>1711321114</v>
+        <v>1713917523</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -7861,6 +8168,7 @@
         </is>
       </c>
       <c r="H232" t="inlineStr"/>
+      <c r="I232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -7879,7 +8187,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>1711321596</v>
+        <v>1713917538</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -7889,10 +8197,11 @@
       <c r="F233" t="inlineStr"/>
       <c r="G233" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>BedroomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H233" t="inlineStr"/>
+      <c r="I233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -7911,7 +8220,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>1711321620</v>
+        <v>1713926228</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -7921,10 +8230,11 @@
       <c r="F234" t="inlineStr"/>
       <c r="G234" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>BedroomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H234" t="inlineStr"/>
+      <c r="I234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -7943,7 +8253,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>1711322979</v>
+        <v>1713926247</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -7957,6 +8267,7 @@
         </is>
       </c>
       <c r="H235" t="inlineStr"/>
+      <c r="I235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -7975,7 +8286,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>1711323020</v>
+        <v>1713926265</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
@@ -7985,10 +8296,15 @@
       <c r="F236" t="inlineStr"/>
       <c r="G236" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dim</t>
+          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H236" t="inlineStr"/>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -8007,7 +8323,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>1711323046</v>
+        <v>1714001724</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
@@ -8017,10 +8333,11 @@
       <c r="F237" t="inlineStr"/>
       <c r="G237" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dark</t>
+          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H237" t="inlineStr"/>
+      <c r="I237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -8039,7 +8356,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>1711330580</v>
+        <v>1714001745</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
@@ -8053,6 +8370,7 @@
         </is>
       </c>
       <c r="H238" t="inlineStr"/>
+      <c r="I238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -8071,7 +8389,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>1711330621</v>
+        <v>1714001765</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
@@ -8081,10 +8399,11 @@
       <c r="F239" t="inlineStr"/>
       <c r="G239" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>BedroomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H239" t="inlineStr"/>
+      <c r="I239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -8103,7 +8422,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>1711330651</v>
+        <v>1714003979</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
@@ -8113,10 +8432,11 @@
       <c r="F240" t="inlineStr"/>
       <c r="G240" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>BedroomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H240" t="inlineStr"/>
+      <c r="I240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -8135,7 +8455,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>1711410502</v>
+        <v>1714004002</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
@@ -8145,10 +8465,11 @@
       <c r="F241" t="inlineStr"/>
       <c r="G241" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>BedroomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H241" t="inlineStr"/>
+      <c r="I241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -8167,7 +8488,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>1711410517</v>
+        <v>1714004573</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
@@ -8181,6 +8502,7 @@
         </is>
       </c>
       <c r="H242" t="inlineStr"/>
+      <c r="I242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -8199,7 +8521,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>1711410529</v>
+        <v>1714004587</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
@@ -8209,10 +8531,11 @@
       <c r="F243" t="inlineStr"/>
       <c r="G243" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dark</t>
+          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H243" t="inlineStr"/>
+      <c r="I243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -8231,7 +8554,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>1711411173</v>
+        <v>1714004600</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
@@ -8241,10 +8564,11 @@
       <c r="F244" t="inlineStr"/>
       <c r="G244" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dim</t>
+          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H244" t="inlineStr"/>
+      <c r="I244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -8263,7 +8587,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>1711411185</v>
+        <v>1714006202</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -8277,6 +8601,7 @@
         </is>
       </c>
       <c r="H245" t="inlineStr"/>
+      <c r="I245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -8295,7 +8620,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>1711411196</v>
+        <v>1714006216</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
@@ -8305,10 +8630,11 @@
       <c r="F246" t="inlineStr"/>
       <c r="G246" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
+          <t>BedroomTwo.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H246" t="inlineStr"/>
+      <c r="I246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -8327,7 +8653,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>1711412993</v>
+        <v>1714006231</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
@@ -8337,10 +8663,11 @@
       <c r="F247" t="inlineStr"/>
       <c r="G247" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
+          <t>BedroomTwo.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H247" t="inlineStr"/>
+      <c r="I247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -8359,7 +8686,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>1711413012</v>
+        <v>1714013002</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
@@ -8373,6 +8700,7 @@
         </is>
       </c>
       <c r="H248" t="inlineStr"/>
+      <c r="I248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -8391,7 +8719,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>1711413025</v>
+        <v>1714013023</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
@@ -8401,10 +8729,11 @@
       <c r="F249" t="inlineStr"/>
       <c r="G249" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dark</t>
+          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H249" t="inlineStr"/>
+      <c r="I249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -8423,7 +8752,7 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>1711422020</v>
+        <v>1714013050</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
@@ -8433,10 +8762,15 @@
       <c r="F250" t="inlineStr"/>
       <c r="G250" t="inlineStr">
         <is>
-          <t>BedroomTwo.Brightness.state: Dim</t>
+          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H250" t="inlineStr"/>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -8455,7 +8789,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>1711422036</v>
+        <v>1714087910</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
@@ -8469,6 +8803,7 @@
         </is>
       </c>
       <c r="H251" t="inlineStr"/>
+      <c r="I251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -8487,7 +8822,7 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>1711422052</v>
+        <v>1714087926</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
@@ -8497,10 +8832,345 @@
       <c r="F252" t="inlineStr"/>
       <c r="G252" t="inlineStr">
         <is>
+          <t>BedroomTwo.Brightness.state: Dim</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr"/>
+      <c r="I252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D253" t="n">
+        <v>1714087940</v>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr"/>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Brightness.state: Dark</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr"/>
+      <c r="I253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D254" t="n">
+        <v>1714088663</v>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr"/>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Brightness.state: Dim</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr"/>
+      <c r="I254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D255" t="n">
+        <v>1714088676</v>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr"/>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr"/>
+      <c r="I255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D256" t="n">
+        <v>1714088687</v>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr"/>
+      <c r="G256" t="inlineStr">
+        <is>
           <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
-      <c r="H252" t="inlineStr"/>
+      <c r="H256" t="inlineStr"/>
+      <c r="I256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D257" t="n">
+        <v>1714090459</v>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr"/>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr"/>
+      <c r="I257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D258" t="n">
+        <v>1714090474</v>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr"/>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Brightness.state: Dim</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr"/>
+      <c r="I258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D259" t="n">
+        <v>1714090497</v>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr"/>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Brightness.state: Dark</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr"/>
+      <c r="I259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D260" t="n">
+        <v>1714098934</v>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr"/>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Brightness.state: Dim</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr"/>
+      <c r="I260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D261" t="n">
+        <v>1714098954</v>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr"/>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Brightness.state: ComfortableBrightness</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr"/>
+      <c r="I261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D262" t="n">
+        <v>1714098971</v>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr"/>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Brightness.state: ExcessivelyBright</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr"/>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
